--- a/test_report.xlsx
+++ b/test_report.xlsx
@@ -438,7 +438,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3">
@@ -448,7 +448,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>100</v>
+        <v>222141.25</v>
       </c>
     </row>
     <row r="4">
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>100</v>
+        <v>2076.09</v>
       </c>
     </row>
   </sheetData>
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,14 +495,131 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Espresso</t>
+          <t>Waffles</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C2" t="n">
-        <v>100</v>
+        <v>9552</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Caramel Syrup</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>18</v>
+      </c>
+      <c r="C3" t="n">
+        <v>8442</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Iced Latte</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>25</v>
+      </c>
+      <c r="C4" t="n">
+        <v>7850</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Berry Shake</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>17</v>
+      </c>
+      <c r="C5" t="n">
+        <v>7072</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Bagel</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n">
+        <v>7008</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Cold Brew</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>16</v>
+      </c>
+      <c r="C7" t="n">
+        <v>6768</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Chai Tea</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>15</v>
+      </c>
+      <c r="C8" t="n">
+        <v>6420</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Extra Shot</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>13</v>
+      </c>
+      <c r="C9" t="n">
+        <v>6409</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Almond Milk</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>17</v>
+      </c>
+      <c r="C10" t="n">
+        <v>6324</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Garlic Bread</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>15</v>
+      </c>
+      <c r="C11" t="n">
+        <v>6210</v>
       </c>
     </row>
   </sheetData>
@@ -516,7 +633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,13 +656,91 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Add-ons</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>114</v>
+      </c>
+      <c r="C2" t="n">
+        <v>41441</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Cold Beverages</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>150</v>
+      </c>
+      <c r="C3" t="n">
+        <v>40583</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Breakfast</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>118</v>
+      </c>
+      <c r="C4" t="n">
+        <v>39305</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Hot Beverages</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>118</v>
+      </c>
+      <c r="C5" t="n">
+        <v>31765</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Desserts</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>103</v>
+      </c>
+      <c r="C6" t="n">
+        <v>23101</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Mains</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>86</v>
+      </c>
+      <c r="C7" t="n">
+        <v>23031</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>Coffee</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B8" t="n">
         <v>2</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C8" t="n">
         <v>100</v>
       </c>
     </row>
@@ -560,7 +755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -583,13 +778,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>212716.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3" t="n">
+        <v>9325</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C4" t="n">
         <v>100</v>
       </c>
     </row>
